--- a/feedback_forms/034_public_library_usage_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/034_public_library_usage_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>services_used</t>
+          <t>Services Used</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>contact_method</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Contact Method</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>Contact Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_notes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>Contact Notes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_notes</t>
+          <t>contact_method_other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact_notes</t>
+          <t>Other Contact Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_method_other</t>
+          <t>contact_email_other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact_method_other</t>
+          <t>Other Contact Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>contact_phone_other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>Other Contact Phone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>contact_notes_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>Other Contact Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_email_other</t>
+          <t>public_library_usage_other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>contact_email_other</t>
+          <t>Other Public Library Usage</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_phone_other</t>
+          <t>services_used_other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>contact_phone_other</t>
+          <t>Other Services Used</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_notes_other</t>
+          <t>suggestions_other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>contact_phone_other</t>
+          <t>Other Suggestions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>contact_method_other_other</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>public_library_usage_other</t>
+          <t>contact_method_additional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>public_library_usage_other</t>
+          <t>Additional Contact Method</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,39 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>services_used_other</t>
+          <t>public_library_usage_additional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>services_used_other</t>
+          <t>Additional Public Library Usage</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>suggestions_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>suggestions_other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -960,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -993,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1010,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1065,6 +1042,57 @@
         </is>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>contact_method_additional_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>contact_form</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Contact Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>contact_method_additional_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>contact_method_additional_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>phone_call</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Phone Call</t>
         </is>
